--- a/experiment/DAT_bestx4/Test/results_table.xlsx
+++ b/experiment/DAT_bestx4/Test/results_table.xlsx
@@ -570,38 +570,38 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>32.200/
-0.8926</t>
+          <t>32.257/
+0.8933</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>28.612/
-0.7815</t>
+          <t>28.648/
+0.7822</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>27.586/
-0.7373</t>
+          <t>27.604/
+0.7380</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>26.073/
-0.7845</t>
+          <t>26.125/
+0.7864</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>30.445/
-0.9075</t>
+          <t>30.506/
+0.9083</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>28.983/
-0.8207</t>
+          <t>29.028/
+0.8216</t>
         </is>
       </c>
     </row>
